--- a/AAII_Financials/Quarterly/SPHR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPHR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>SPHR</t>
   </si>
@@ -656,301 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
-      </c>
-      <c r="J7" s="2">
-        <v>45565</v>
       </c>
       <c r="K7" s="2">
         <v>45565</v>
       </c>
       <c r="L7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="M7" s="2">
         <v>45473</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45382</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>313600</v>
+      </c>
+      <c r="E8" s="3">
         <v>386400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>394300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>262500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>282700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>280600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>308300</v>
-      </c>
-      <c r="J8" s="3">
-        <v>227900</v>
       </c>
       <c r="K8" s="3">
         <v>227900</v>
       </c>
       <c r="L8" s="3">
+        <v>227900</v>
+      </c>
+      <c r="M8" s="3">
         <v>273400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>321300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>118000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>162100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>159500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>123100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>610100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>352500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>575900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>294500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>260600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>214300</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>151100</v>
+      </c>
+      <c r="E9" s="3">
         <v>169600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>156900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>137000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>131300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>158300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>163300</v>
-      </c>
-      <c r="J9" s="3">
-        <v>139700</v>
       </c>
       <c r="K9" s="3">
         <v>139700</v>
       </c>
       <c r="L9" s="3">
+        <v>139700</v>
+      </c>
+      <c r="M9" s="3">
         <v>149500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>154000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>84500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>93700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>90400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>75400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>319000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>448600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>623000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>153000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>120500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>102100</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>162600</v>
+      </c>
+      <c r="E10" s="3">
         <v>216800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>237400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>125500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>151400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>122300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>145000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>88200</v>
       </c>
       <c r="K10" s="3">
         <v>88200</v>
       </c>
       <c r="L10" s="3">
+        <v>88200</v>
+      </c>
+      <c r="M10" s="3">
         <v>129600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>167300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>33500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>68400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>69100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>47700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>291100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-96100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-47100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>141500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>140100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>112200</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,138 +1121,147 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>5500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>71300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-341700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>183100</v>
-      </c>
-      <c r="J14" s="3">
-        <v>4800</v>
       </c>
       <c r="K14" s="3">
         <v>4800</v>
       </c>
       <c r="L14" s="3">
+        <v>4800</v>
+      </c>
+      <c r="M14" s="3">
         <v>5800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-41700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>18500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-2000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>51400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>9100</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>7800</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>84300</v>
+      </c>
+      <c r="E15" s="3">
         <v>84400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>84200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>84100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>83900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>84200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>83300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>81900</v>
       </c>
       <c r="K15" s="3">
         <v>81900</v>
       </c>
       <c r="L15" s="3">
+        <v>81900</v>
+      </c>
+      <c r="M15" s="3">
         <v>82300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>79900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>14300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>7400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>6100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>22600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>20500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>42600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>29400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>28300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>39600</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>374900</v>
+      </c>
+      <c r="E17" s="3">
         <v>376100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>367200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>321100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>328600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>357200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>268800</v>
-      </c>
-      <c r="J17" s="3">
-        <v>340900</v>
       </c>
       <c r="K17" s="3">
         <v>340900</v>
       </c>
       <c r="L17" s="3">
+        <v>340900</v>
+      </c>
+      <c r="M17" s="3">
         <v>339400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>357400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>185900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>245300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>209300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>174200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>775800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>351700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>646200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>377800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>304600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>253100</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-61300</v>
+      </c>
+      <c r="E18" s="3">
         <v>10300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>27100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-58600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-45900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-76600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>39500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-113000</v>
       </c>
       <c r="K18" s="3">
         <v>-113000</v>
       </c>
       <c r="L18" s="3">
+        <v>-113000</v>
+      </c>
+      <c r="M18" s="3">
         <v>-7100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-36000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-67900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-83200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-49800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-51100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-165700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-70300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-83300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-44000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-38800</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,333 +1444,349 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>500</v>
       </c>
       <c r="K20" s="3">
         <v>500</v>
       </c>
       <c r="L20" s="3">
+        <v>500</v>
+      </c>
+      <c r="M20" s="3">
         <v>1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-20700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>26000</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E21" s="3">
         <v>93600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>111800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>25300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>37700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>124100</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-31600</v>
       </c>
       <c r="K21" s="3">
         <v>-31600</v>
       </c>
       <c r="L21" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="M21" s="3">
         <v>73300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>40800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-55100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-79300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-16200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-43100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>20200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-31000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-56900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-18600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E22" s="3">
         <v>8000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>25900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>26200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>30400</v>
-      </c>
-      <c r="J22" s="3">
-        <v>27000</v>
       </c>
       <c r="K22" s="3">
         <v>27000</v>
       </c>
       <c r="L22" s="3">
+        <v>27000</v>
+      </c>
+      <c r="M22" s="3">
         <v>26900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>27100</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>2200</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>5500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>16500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>9200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-65300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>22400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-136700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>273800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-102300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-168300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-138200</v>
       </c>
       <c r="K23" s="3">
         <v>-138200</v>
       </c>
       <c r="L23" s="3">
+        <v>-138200</v>
+      </c>
+      <c r="M23" s="3">
         <v>-93200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-63100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-23200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-102700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-48400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-48100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-167700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-13900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-107500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-95600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-50300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-4800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-42300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-35500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>121900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-20300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-42400</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-33000</v>
       </c>
       <c r="K24" s="3">
         <v>-33000</v>
       </c>
       <c r="L24" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="M24" s="3">
         <v>-22000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-15900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-90300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>11300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-29800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>6300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-16500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-18900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-10000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6600</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="E26" s="3">
         <v>4500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>64700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-101200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>151800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-82000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-126000</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-105300</v>
       </c>
       <c r="K26" s="3">
         <v>-105300</v>
       </c>
       <c r="L26" s="3">
+        <v>-105300</v>
+      </c>
+      <c r="M26" s="3">
         <v>-71200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-47200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>67100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-114000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-46300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-137900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-20300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-91100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-76700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-40300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-25800</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>64700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-101200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>151800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-82000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-126000</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-105300</v>
       </c>
       <c r="K27" s="3">
         <v>-105300</v>
       </c>
       <c r="L27" s="3">
+        <v>-105300</v>
+      </c>
+      <c r="M27" s="3">
         <v>-46600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-47200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>66400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-56800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-30300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-47000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-140900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-19600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-93300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-79200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-38300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2026,43 +2087,46 @@
         <v>0</v>
       </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>24600</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>57200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>103500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>1100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-60000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>2600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>13700</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-500</v>
       </c>
       <c r="K32" s="3">
         <v>-500</v>
       </c>
       <c r="L32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>20700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-26000</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>64700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-101200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>151800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-82000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-126000</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-105300</v>
       </c>
       <c r="K33" s="3">
         <v>-105300</v>
       </c>
       <c r="L33" s="3">
+        <v>-105300</v>
+      </c>
+      <c r="M33" s="3">
         <v>-46600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-47200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>66400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-56800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>73300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-45900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-200900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-17000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-79600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-79200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-38300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>64700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-101200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>151800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-82000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-126000</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-105300</v>
       </c>
       <c r="K35" s="3">
         <v>-105300</v>
       </c>
       <c r="L35" s="3">
+        <v>-105300</v>
+      </c>
+      <c r="M35" s="3">
         <v>-46600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-47200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>66400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-56800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>73300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-45900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-200900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-17000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-79600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-79200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-38300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
-      </c>
-      <c r="J38" s="2">
-        <v>45565</v>
       </c>
       <c r="K38" s="2">
         <v>45565</v>
       </c>
       <c r="L38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="M38" s="2">
         <v>45473</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45382</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,73 +2657,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>551000</v>
+      </c>
+      <c r="E41" s="3">
         <v>629100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>507800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>384800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>355700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>465000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>502000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>539600</v>
       </c>
       <c r="K41" s="3">
         <v>539600</v>
       </c>
       <c r="L41" s="3">
+        <v>539600</v>
+      </c>
+      <c r="M41" s="3">
         <v>559800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>680600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>433500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>217600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>432200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>441400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1552700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>999100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1258100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1331500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1517000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1277700</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,115 +2791,121 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>165100</v>
+      </c>
+      <c r="E43" s="3">
         <v>201800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>196100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>181200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>162200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>192200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>180400</v>
-      </c>
-      <c r="J43" s="3">
-        <v>126700</v>
       </c>
       <c r="K43" s="3">
         <v>126700</v>
       </c>
       <c r="L43" s="3">
+        <v>126700</v>
+      </c>
+      <c r="M43" s="3">
         <v>241500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>200500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>184500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>263100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>217100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>209500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>344500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>327400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>249600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>231400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>309500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>153800</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E44" s="3">
         <v>18300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>14500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>12600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>12800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>13200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12600</v>
-      </c>
-      <c r="J44" s="3">
-        <v>14100</v>
       </c>
       <c r="K44" s="3">
         <v>14100</v>
       </c>
       <c r="L44" s="3">
+        <v>14100</v>
+      </c>
+      <c r="M44" s="3">
         <v>11900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2400</v>
       </c>
-      <c r="O44" s="3" t="s">
+      <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
       <c r="Q44" s="3">
         <v>0</v>
       </c>
@@ -2831,333 +2927,351 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E45" s="3">
         <v>26900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>39800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>40400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>29900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>20000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>15100</v>
       </c>
       <c r="K45" s="3">
         <v>15100</v>
       </c>
       <c r="L45" s="3">
+        <v>15100</v>
+      </c>
+      <c r="M45" s="3">
         <v>8200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>518700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>266900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>190100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>347400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>131700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>127700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>126300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>132300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>109300</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>784000</v>
+      </c>
+      <c r="E46" s="3">
         <v>903600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>810200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>666400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>595400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>735100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>761000</v>
-      </c>
-      <c r="J46" s="3">
-        <v>736100</v>
       </c>
       <c r="K46" s="3">
         <v>736100</v>
       </c>
       <c r="L46" s="3">
+        <v>736100</v>
+      </c>
+      <c r="M46" s="3">
         <v>865700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>916100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>674000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1190100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>916200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>840900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1218700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1458200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1635400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1689100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1872700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1540800</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E47" s="3">
         <v>37700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>38700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>40400</v>
-      </c>
-      <c r="G47" s="3">
-        <v>41300</v>
       </c>
       <c r="H47" s="3">
         <v>41300</v>
       </c>
       <c r="I47" s="3">
+        <v>41300</v>
+      </c>
+      <c r="J47" s="3">
         <v>40400</v>
-      </c>
-      <c r="J47" s="3">
-        <v>31400</v>
       </c>
       <c r="K47" s="3">
         <v>31400</v>
       </c>
       <c r="L47" s="3">
+        <v>31400</v>
+      </c>
+      <c r="M47" s="3">
         <v>27800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>51800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>50800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>93400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>41100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>45300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>46700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>48200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>49300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>273600</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2646600</v>
+      </c>
+      <c r="E48" s="3">
         <v>2718300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2802000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2863200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2940700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3059100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3129700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>3195700</v>
       </c>
       <c r="K48" s="3">
         <v>3195700</v>
       </c>
       <c r="L48" s="3">
+        <v>3195700</v>
+      </c>
+      <c r="M48" s="3">
         <v>3264900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3329600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3561100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4029800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4008800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3684500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2301700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3169700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2944900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2698200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2436900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2127100</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>363300</v>
+      </c>
+      <c r="E49" s="3">
         <v>364900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>366600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>368200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>435300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>437000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>438600</v>
-      </c>
-      <c r="J49" s="3">
-        <v>500300</v>
       </c>
       <c r="K49" s="3">
         <v>500300</v>
       </c>
       <c r="L49" s="3">
+        <v>500300</v>
+      </c>
+      <c r="M49" s="3">
         <v>502100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>472400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>473900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>581300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>717400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>722200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>705700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>741100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>746000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>750200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>764300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>265700</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,73 +3403,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E52" s="3">
         <v>29700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>31400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>44600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>43100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>30700</v>
       </c>
       <c r="K52" s="3">
         <v>30700</v>
       </c>
       <c r="L52" s="3">
+        <v>30700</v>
+      </c>
+      <c r="M52" s="3">
         <v>34300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>99000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>104800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>108400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>206600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>177600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1734200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>166200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>150000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>152200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>173500</v>
       </c>
-      <c r="W52" s="3" t="s">
+      <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4036000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4222700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4209900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4138600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4199100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4447600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4515300</v>
-      </c>
-      <c r="J54" s="3">
-        <v>4592700</v>
       </c>
       <c r="K54" s="3">
         <v>4592700</v>
       </c>
       <c r="L54" s="3">
+        <v>4592700</v>
+      </c>
+      <c r="M54" s="3">
         <v>4787900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4868800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4864700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6049500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5849700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5426100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5522200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5580400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5523100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5337900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5289900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4104200</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,398 +3661,417 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E57" s="3">
         <v>36500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>30800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>33900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>33600</v>
-      </c>
-      <c r="J57" s="3">
-        <v>35400</v>
       </c>
       <c r="K57" s="3">
         <v>35400</v>
       </c>
       <c r="L57" s="3">
+        <v>35400</v>
+      </c>
+      <c r="M57" s="3">
         <v>18900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>73700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>32600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>127900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>106300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>759400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>40400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>43800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>26500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>26600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>10400</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>72300</v>
+      </c>
+      <c r="E58" s="3">
         <v>74200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>80200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>105000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>76300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>822700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>848400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>849900</v>
       </c>
       <c r="K58" s="3">
         <v>849900</v>
       </c>
       <c r="L58" s="3">
+        <v>849900</v>
+      </c>
+      <c r="M58" s="3">
         <v>868000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>887500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>116200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>144800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>102500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>86200</v>
-      </c>
-      <c r="R58" s="3">
-        <v>66000</v>
       </c>
       <c r="S58" s="3">
         <v>66000</v>
       </c>
       <c r="T58" s="3">
+        <v>66000</v>
+      </c>
+      <c r="U58" s="3">
         <v>56500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>55200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>54000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>426300</v>
+      </c>
+      <c r="E59" s="3">
         <v>508400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>486400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>411000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>310000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>369500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>343900</v>
-      </c>
-      <c r="J59" s="3">
-        <v>310900</v>
       </c>
       <c r="K59" s="3">
         <v>310900</v>
       </c>
       <c r="L59" s="3">
+        <v>310900</v>
+      </c>
+      <c r="M59" s="3">
         <v>309200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>289400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>366800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>947800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>734000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>727700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1183500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>858500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>769500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>672200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>649300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>498500</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>640400</v>
+      </c>
+      <c r="E60" s="3">
         <v>742700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>743400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>697200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>526900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1381100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1371700</v>
-      </c>
-      <c r="J60" s="3">
-        <v>1315400</v>
       </c>
       <c r="K60" s="3">
         <v>1315400</v>
       </c>
       <c r="L60" s="3">
+        <v>1315400</v>
+      </c>
+      <c r="M60" s="3">
         <v>1373700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1398600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>642900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1400000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>964500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>920100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>961100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>964900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>869800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>753800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>729900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>513300</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>841000</v>
+      </c>
+      <c r="E61" s="3">
         <v>864200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>881300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>895800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>942400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>639100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>640700</v>
-      </c>
-      <c r="J61" s="3">
-        <v>648200</v>
       </c>
       <c r="K61" s="3">
         <v>648200</v>
       </c>
       <c r="L61" s="3">
+        <v>648200</v>
+      </c>
+      <c r="M61" s="3">
         <v>650800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>652500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1209900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2124400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1885300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1652600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>929500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1584100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1606800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1621200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1650600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>657000</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>191500</v>
+      </c>
+      <c r="E62" s="3">
         <v>201300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>160100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>175300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>165500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>157400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>132900</v>
-      </c>
-      <c r="J62" s="3">
-        <v>122300</v>
       </c>
       <c r="K62" s="3">
         <v>122300</v>
       </c>
       <c r="L62" s="3">
+        <v>122300</v>
+      </c>
+      <c r="M62" s="3">
         <v>102500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>119100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>87500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>142500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>790800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>748900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1472000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>772000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>776700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>726500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>591100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>301200</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1808100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1974800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1976700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1983500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1885400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2305600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2313900</v>
-      </c>
-      <c r="J66" s="3">
-        <v>2278500</v>
       </c>
       <c r="K66" s="3">
         <v>2278500</v>
       </c>
       <c r="L66" s="3">
+        <v>2278500</v>
+      </c>
+      <c r="M66" s="3">
         <v>2372300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2425200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2228800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3876700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3843800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3519100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3558900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3473600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3411300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3255100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3121400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1498700</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-220300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-182000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-186400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-251200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-150000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-301800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-219800</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-93900</v>
       </c>
       <c r="K72" s="3">
         <v>-93900</v>
       </c>
       <c r="L72" s="3">
+        <v>-93900</v>
+      </c>
+      <c r="M72" s="3">
         <v>11400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>58000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>278500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-324800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-267900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-335500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-290700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-190800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-173300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-175600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-96300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-152400</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2227900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2247900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2233200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2155100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2313700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2142100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2201400</v>
-      </c>
-      <c r="J76" s="3">
-        <v>2314200</v>
       </c>
       <c r="K76" s="3">
         <v>2314200</v>
       </c>
       <c r="L76" s="3">
+        <v>2314200</v>
+      </c>
+      <c r="M76" s="3">
         <v>2415600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2443600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2635900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2020600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2005900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1907000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1963200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2106800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2111800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2082900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2168500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2605500</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
-      </c>
-      <c r="J80" s="2">
-        <v>45565</v>
       </c>
       <c r="K80" s="2">
         <v>45565</v>
       </c>
       <c r="L80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="M80" s="2">
         <v>45473</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45382</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>64700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-101200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>151800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-82000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-126000</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-105300</v>
       </c>
       <c r="K81" s="3">
         <v>-105300</v>
       </c>
       <c r="L81" s="3">
+        <v>-105300</v>
+      </c>
+      <c r="M81" s="3">
         <v>-46600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-47200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>66400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-56800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>73300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-45900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-200900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-17000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-79600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-79200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-38300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-27000</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,73 +5214,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E83" s="3">
         <v>82600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>81600</v>
-      </c>
-      <c r="F83" s="3">
-        <v>80100</v>
       </c>
       <c r="G83" s="3">
         <v>80100</v>
       </c>
       <c r="H83" s="3">
-        <v>80900</v>
+        <v>80100</v>
       </c>
       <c r="I83" s="3">
         <v>80900</v>
       </c>
       <c r="J83" s="3">
-        <v>79100</v>
+        <v>80900</v>
       </c>
       <c r="K83" s="3">
         <v>79100</v>
       </c>
       <c r="L83" s="3">
+        <v>79100</v>
+      </c>
+      <c r="M83" s="3">
         <v>13500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>74900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>29000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>35600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>29100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>29800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>124600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>28600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>60000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>29400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>28300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>39600</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="E89" s="3">
         <v>136200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>180200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>115800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-59100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6700</v>
-      </c>
-      <c r="J89" s="3">
-        <v>34100</v>
       </c>
       <c r="K89" s="3">
         <v>34100</v>
       </c>
       <c r="L89" s="3">
+        <v>34100</v>
+      </c>
+      <c r="M89" s="3">
         <v>-72400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>101000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-94600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>82900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>136100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-81200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>141300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-26600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>132800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>7000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>55400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-11600</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-30400</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-18500</v>
       </c>
       <c r="K91" s="3">
         <v>-18500</v>
       </c>
       <c r="L91" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="M91" s="3">
         <v>-14800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-190000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-243800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-288700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-270100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-240200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-203400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-175800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-137300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-131400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-102800</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-15300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>34000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-40600</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-19600</v>
       </c>
       <c r="K94" s="3">
         <v>-19600</v>
       </c>
       <c r="L94" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="M94" s="3">
         <v>-24900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-21200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>66500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-249600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-290700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-285200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-804200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-215400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-332500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-146300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-165400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-100600</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5822,8 +6056,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,199 +6284,211 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-29900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-22300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-41300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-81000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-84800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-26300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2300</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-35600</v>
       </c>
       <c r="K100" s="3">
         <v>-35600</v>
       </c>
       <c r="L100" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="M100" s="3">
         <v>-23300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>50900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-28700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>249200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-20000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-30400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-19900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-57600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-44800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>15500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1400</v>
-      </c>
-      <c r="F101" s="3">
-        <v>1100</v>
       </c>
       <c r="G101" s="3">
         <v>1100</v>
       </c>
       <c r="H101" s="3">
-        <v>-100</v>
+        <v>1100</v>
       </c>
       <c r="I101" s="3">
         <v>-100</v>
       </c>
       <c r="J101" s="3">
-        <v>-700</v>
+        <v>-100</v>
       </c>
       <c r="K101" s="3">
         <v>-700</v>
       </c>
       <c r="L101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-400</v>
-      </c>
-      <c r="V101" s="3">
-        <v>100</v>
       </c>
       <c r="W101" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-78100</v>
+      </c>
+      <c r="E102" s="3">
         <v>108900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>123000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>29300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-109300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-37400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-37600</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-20000</v>
       </c>
       <c r="K102" s="3">
         <v>-20000</v>
       </c>
       <c r="L102" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="M102" s="3">
         <v>-120700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>66100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>22600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-195600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>94800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-387100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-694000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-261300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-258000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-184500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-86400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-134800</v>
       </c>
     </row>
